--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -431,7 +431,7 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -558,7 +558,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1: provider</t>
+          <t>iapd.adv.custodians.v1: provider</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1: kind</t>
+          <t>iapd.adv.custodians.v1: kind</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -582,19 +582,19 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1: one record is</t>
+          <t>iapd.adv.custodians.v1: one record is</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>one custody row (the filing and the row's number in the monthly file); a custodian's rows join by LEI or SEC broker-dealer number</t>
+          <t>one custodian named in one monthly file (the file's month end and custodian_id, from its first custody row in the file); a custodian's records join by LEI or SEC broker-dealer number</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1: one publication is</t>
+          <t>iapd.adv.custodians.v1: one publication is</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -606,19 +606,19 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1: a file covers</t>
+          <t>iapd.adv.custodians.v1: a file covers</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>the custodians holding 10% or more of an adviser's separately managed account assets, per filing that month; no retirement by absence</t>
+          <t>the custodians holding 10% or more of an adviser's separately managed account assets, named in one month's filings; no retirement by absence</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1: set aside without stopping the run</t>
+          <t>iapd.adv.custodians.v1: set aside without stopping the run</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -638,15 +638,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="57" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -904,7 +904,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -925,14 +925,14 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.fields.name</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -957,14 +957,14 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.address</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -989,14 +989,14 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.address</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1021,71 +1021,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.fields.address</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>iapd.adv.custody.v1</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>relationship CUSTODIAN</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>filing_id</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Link from iapd.adv.filings.v1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>iapd.adv.custody.v1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>relationship CUSTODIAN</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>filing_id, row</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Link to iapd.adv.custody.v1</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.relationships</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.address</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1039,7 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1222,7 +1158,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1252,14 +1188,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.identifiers.lei</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.lei</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1285,7 +1221,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custody.v1.contract.adapter.identifiers.bd_number</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.bd_number</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1239,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1367,7 +1303,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1387,7 +1323,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>quality.iapd.adv.custody.v1.checks[0]</t>
+          <t>quality.iapd.adv.custodians.v1.checks[0]</t>
         </is>
       </c>
     </row>
@@ -1405,13 +1341,13 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1491,7 +1427,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1521,7 +1457,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>quality.iapd.adv.custody.v1.checks[0]</t>
+          <t>quality.iapd.adv.custodians.v1.checks[0]</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1528,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1624,7 +1560,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1656,7 +1592,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1688,7 +1624,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1121,7 +1121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.filings.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>No: lookup only</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.identifiers.lei</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.lei</t>
         </is>
       </c>
     </row>
@@ -1163,19 +1163,15 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>bd_number</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>lei</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>lei</t>
-        </is>
-      </c>
+          <t>bd_number</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1187,39 +1183,6 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.lei</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>iapd.adv.custodians.v1</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>bd_number</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>bd_number</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Only with a new dataset code</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.bd_number</t>
         </is>

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -1041,7 +1041,7 @@
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -1126,19 +1126,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>bd_number</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>lei</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>lei</t>
-        </is>
-      </c>
+          <t>bd_number</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1151,7 +1147,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.lei</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.bd_number</t>
         </is>
       </c>
     </row>
@@ -1163,15 +1159,19 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>bd_number</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>bd_number</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>custodian_lei</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.bd_number</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.identifiers.lei</t>
         </is>
       </c>
     </row>

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>quality_custodian_name_present</t>
+          <t>quality_custodian_name_present, invalid_lei_checksum</t>
         </is>
       </c>
     </row>

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -646,7 +646,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.name</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.filings.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.name</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.fields.address</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -638,14 +638,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -904,60 +904,64 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custodians.v1</t>
+          <t>iapd.adv.filings.v1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>relationship CUSTODIAN</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>legal_name</t>
+          <t>published, item</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>Link to iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custodians.v1</t>
+          <t>iapd.adv.filings.v1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>relationship CUSTODIAN</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>each</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>custodians</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>One link per item (item.)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
+          <t>mdm.iapd.adv.filings.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -969,17 +973,13 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>legal_name</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name</t>
         </is>
       </c>
     </row>
@@ -1006,20 +1006,84 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>country</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>MDM field</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>mdm.iapd.adv.custodians.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>one custodian named in one monthly file (the file's month end and custodian_id, from its first custody row in the file); a custodian's records join by LEI or SEC broker-dealer number</t>
+          <t>one custodian (custodian_id, from its first custody row in a file); each monthly file restates it as a new publication; a custodian's records join by LEI or SEC broker-dealer number</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -919,7 +919,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>published, item</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">

--- a/rules/sources/iapd.adv/MAPPING.xlsx
+++ b/rules/sources/iapd.adv/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1681,6 +1683,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
